--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D3">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H3">
         <v>426</v>
